--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T19:29:11+00:00</t>
+    <t>2026-09-03T14:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A profile representing a hematopoietic cell donor registered in the NMDP registry.</t>
+    <t>A profile representing a hematopoietic cell donor registered in the NMDP registry. Donors are identified by having an NMDP GRID identifier. The Patient.id should be the GRID value.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -466,7 +466,7 @@
 </t>
   </si>
   <si>
-    <t>US Core Race</t>
+    <t>(USCDI) US Core Race Extension</t>
   </si>
   <si>
     <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The race codes used to represent these concepts are based upon the [CDC Race and Ethnicity Code Set Version 1.0](http://www.cdc.gov/phin/resources/vocabulary/index.html) which includes over 900 concepts for representing race and ethnicity of which 921 reference race.  The race concepts are grouped by and pre-mapped to the 5 OMB race categories:
@@ -491,7 +491,7 @@
 </t>
   </si>
   <si>
-    <t>US Core Ethnicity</t>
+    <t>(USCDI) US Core ethnicity Extension</t>
   </si>
   <si>
     <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The ethnicity codes used to represent these concepts are based upon the [CDC ethnicity and Ethnicity Code Set Version 1.0](http://www.cdc.gov/phin/resources/vocabulary/index.html) which includes over 900 concepts for representing race and ethnicity of which 43 reference ethnicity.  The ethnicity concepts are grouped by and pre-mapped to the 2 OMB ethnicity categories: - Hispanic or Latino - Not Hispanic or Latino.</t>
@@ -583,7 +583,7 @@
     <t>Donor registry status</t>
   </si>
   <si>
-    <t>The registration status of a donor in the NMDP registry, with an optional available date for temporarily unavailable donors.</t>
+    <t>The current registration status of the donor (e.g., Available, Temporarily Unavailable, Active, Permanently Unavailable).</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -840,55 +840,16 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>Patient.identifier:nmdpDonorId</t>
-  </si>
-  <si>
-    <t>nmdpDonorId</t>
-  </si>
-  <si>
-    <t>NMDP Donor ID</t>
-  </si>
-  <si>
-    <t>The unique identifier assigned to a donor by the National Marrow Donor Program.</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.use</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.type</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.system</t>
-  </si>
-  <si>
-    <t>http://terminology.nmdp.org/identifier/donor</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.value</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.period</t>
-  </si>
-  <si>
-    <t>Patient.identifier:nmdpDonorId.assigner</t>
-  </si>
-  <si>
     <t>Patient.identifier:grid</t>
   </si>
   <si>
     <t>grid</t>
   </si>
   <si>
-    <t>Global Registration Identifier for Donors (GRID)</t>
-  </si>
-  <si>
-    <t>The ISBT 128 Global Registration Identifier for Donors.</t>
+    <t>NMDP GRID (Global Registration Identifier for Donors)</t>
+  </si>
+  <si>
+    <t>The NMDP GRID identifier that uniquely identifies a donor. A 32-character uppercase alphanumeric string (0-9 and A-F, no dashes or spaces), e.g. 99D0BA02660443B585D525525EB3F2D2. System: http://nmdp.org/identifier/grid</t>
   </si>
   <si>
     <t>Patient.identifier:grid.id</t>
@@ -906,7 +867,7 @@
     <t>Patient.identifier:grid.system</t>
   </si>
   <si>
-    <t>http://www.isbt128.org/uri/GRID</t>
+    <t>http://nmdp.org/identifier/grid</t>
   </si>
   <si>
     <t>Patient.identifier:grid.value</t>
@@ -916,6 +877,45 @@
   </si>
   <si>
     <t>Patient.identifier:grid.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId</t>
+  </si>
+  <si>
+    <t>sourceId</t>
+  </si>
+  <si>
+    <t>Donor source ID</t>
+  </si>
+  <si>
+    <t>The source identifier for the donor in the originating registry. System: http://nmdp.org/identifier/source-id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.system</t>
+  </si>
+  <si>
+    <t>http://nmdp.org/identifier/source-id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:sourceId.assigner</t>
   </si>
   <si>
     <t>Patient.active</t>
@@ -1355,10 +1355,10 @@
 dateTime</t>
   </si>
   <si>
-    <t>Indicates if the donor is deceased</t>
-  </si>
-  <si>
-    <t>Indicates if the donor is deceased, either as a boolean flag or a dateTime of death.</t>
+    <t>(USCDI) Indicates if the individual is deceased or not</t>
+  </si>
+  <si>
+    <t>Indicates if the individual is deceased or not.</t>
   </si>
   <si>
     <t>If there's no value in the instance, it means there is no statement on whether or not the individual is deceased. Most systems will interpret the absence of a value as a sign of the person being alive.</t>
@@ -2026,10 +2026,10 @@
 </t>
   </si>
   <si>
-    <t>Donor center managing this donor</t>
-  </si>
-  <si>
-    <t>The NMDP-affiliated organization (typically a donor center) that manages this donor's registration.</t>
+    <t>Donor center (ION/DC ID)</t>
+  </si>
+  <si>
+    <t>The NMDP donor center (identified by ION/DC ID) responsible for this donor.</t>
   </si>
   <si>
     <t>There is only one managing organization for a specific patient record. Other organizations will have their own Patient record, and may use the Link property to join the records together (or a Person resource which can include confidence ratings for the association).</t>
@@ -10090,7 +10090,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>427</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>90</v>
@@ -13370,7 +13370,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>608</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>81</v>

--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:51:12+00:00</t>
+    <t>2026-09-03T16:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
